--- a/app/downloads/esg/c3-under-tree-books-esg-pack.xlsx
+++ b/app/downloads/esg/c3-under-tree-books-esg-pack.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R6a4acb442d4c49da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐棵明細" sheetId="2" r:id="R1acb57ca81b84fdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="盤點紀錄" sheetId="3" r:id="R6c22a5bf1e6c40ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRI 對照" sheetId="4" r:id="Rcd811a0a668047e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="報告書段落" sheetId="5" r:id="R232f82b7a94f463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法與限制" sheetId="6" r:id="R181ded85464740c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R634e9e933a6c4a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐棵明細" sheetId="2" r:id="R50615997f2a246dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="盤點紀錄" sheetId="3" r:id="Rfcd5fb981e4c4f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRI 對照" sheetId="4" r:id="R1800e5b11b1848e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="報告書段落" sheetId="5" r:id="Rda3784289a2b4689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法與限制" sheetId="6" r:id="R3cdd9fc3dd6a496b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
         <x:v>報告期間</x:v>
       </x:c>
       <x:c r="B3" s="20" t="str">
-        <x:v>2026-01-01 至 2026-10-24</x:v>
+        <x:v>2026-06-01 至 2026-10-24</x:v>
       </x:c>
       <x:c r="C3" s="20" t="str">
         <x:v>模擬</x:v>
@@ -642,16 +642,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E2" s="25" t="n">
-        <x:v>121.548879</x:v>
+        <x:v>121.54888</x:v>
       </x:c>
       <x:c r="F2" s="25" t="n">
-        <x:v>25.029347</x:v>
+        <x:v>25.02935</x:v>
       </x:c>
       <x:c r="G2" s="25" t="n">
-        <x:v>305391.22</x:v>
+        <x:v>305391.32</x:v>
       </x:c>
       <x:c r="H2" s="25" t="n">
-        <x:v>2769140.35</x:v>
+        <x:v>2769140.68</x:v>
       </x:c>
       <x:c r="I2" s="26" t="n">
         <x:v>27</x:v>
@@ -688,16 +688,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E3" s="25" t="n">
-        <x:v>121.548845</x:v>
+        <x:v>121.54885</x:v>
       </x:c>
       <x:c r="F3" s="25" t="n">
-        <x:v>25.024014</x:v>
+        <x:v>25.02401</x:v>
       </x:c>
       <x:c r="G3" s="25" t="n">
-        <x:v>305390.19</x:v>
+        <x:v>305390.69</x:v>
       </x:c>
       <x:c r="H3" s="25" t="n">
-        <x:v>2768549.62</x:v>
+        <x:v>2768549.18</x:v>
       </x:c>
       <x:c r="I3" s="26" t="n">
         <x:v>29</x:v>
@@ -718,7 +718,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O3" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211358</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211358</x:v>
       </x:c>
       <x:c r="P3" s="2" t="str">
         <x:v>2023-08-01</x:v>
@@ -738,16 +738,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E4" s="25" t="n">
-        <x:v>121.548803</x:v>
+        <x:v>121.5488</x:v>
       </x:c>
       <x:c r="F4" s="25" t="n">
-        <x:v>25.022267</x:v>
+        <x:v>25.02227</x:v>
       </x:c>
       <x:c r="G4" s="25" t="n">
-        <x:v>305386.73</x:v>
+        <x:v>305386.43</x:v>
       </x:c>
       <x:c r="H4" s="25" t="n">
-        <x:v>2768356.1</x:v>
+        <x:v>2768356.43</x:v>
       </x:c>
       <x:c r="I4" s="26" t="n">
         <x:v>39</x:v>
@@ -768,7 +768,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O4" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211455</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211455</x:v>
       </x:c>
       <x:c r="P4" s="2" t="str">
         <x:v>2023-08-04</x:v>
@@ -788,16 +788,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E5" s="25" t="n">
-        <x:v>121.548574</x:v>
+        <x:v>121.54857</x:v>
       </x:c>
       <x:c r="F5" s="25" t="n">
-        <x:v>25.022571</x:v>
+        <x:v>25.02257</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
-        <x:v>305363.48</x:v>
+        <x:v>305363.08</x:v>
       </x:c>
       <x:c r="H5" s="25" t="n">
-        <x:v>2768389.68</x:v>
+        <x:v>2768389.57</x:v>
       </x:c>
       <x:c r="I5" s="26" t="n">
         <x:v>26</x:v>
@@ -818,7 +818,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O5" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212037</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212037</x:v>
       </x:c>
       <x:c r="P5" s="2" t="str">
         <x:v>2023-08-04</x:v>
@@ -838,16 +838,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E6" s="25" t="n">
-        <x:v>121.548628</x:v>
+        <x:v>121.54863</x:v>
       </x:c>
       <x:c r="F6" s="25" t="n">
-        <x:v>25.025209</x:v>
+        <x:v>25.02521</x:v>
       </x:c>
       <x:c r="G6" s="25" t="n">
-        <x:v>305367.75</x:v>
+        <x:v>305367.95</x:v>
       </x:c>
       <x:c r="H6" s="25" t="n">
-        <x:v>2768681.9</x:v>
+        <x:v>2768682.01</x:v>
       </x:c>
       <x:c r="I6" s="26" t="n">
         <x:v>28</x:v>
@@ -887,13 +887,13 @@
         <x:v>121.54865</x:v>
       </x:c>
       <x:c r="F7" s="25" t="n">
-        <x:v>25.029461</x:v>
+        <x:v>25.02946</x:v>
       </x:c>
       <x:c r="G7" s="25" t="n">
         <x:v>305368.06</x:v>
       </x:c>
       <x:c r="H7" s="25" t="n">
-        <x:v>2769152.88</x:v>
+        <x:v>2769152.77</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
         <x:v>33</x:v>
@@ -914,7 +914,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O7" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212328</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212328</x:v>
       </x:c>
       <x:c r="P7" s="2" t="str">
         <x:v>2023-08-12</x:v>
@@ -934,16 +934,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E8" s="25" t="n">
-        <x:v>121.548665</x:v>
+        <x:v>121.54866</x:v>
       </x:c>
       <x:c r="F8" s="25" t="n">
-        <x:v>25.031591</x:v>
+        <x:v>25.03159</x:v>
       </x:c>
       <x:c r="G8" s="25" t="n">
-        <x:v>305368.62</x:v>
+        <x:v>305368.12</x:v>
       </x:c>
       <x:c r="H8" s="25" t="n">
-        <x:v>2769388.82</x:v>
+        <x:v>2769388.71</x:v>
       </x:c>
       <x:c r="I8" s="26" t="n">
         <x:v>30</x:v>
@@ -964,7 +964,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O8" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212425</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212425</x:v>
       </x:c>
       <x:c r="P8" s="2" t="str">
         <x:v>2023-08-11</x:v>
@@ -984,16 +984,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E9" s="25" t="n">
-        <x:v>121.548828</x:v>
+        <x:v>121.54883</x:v>
       </x:c>
       <x:c r="F9" s="25" t="n">
-        <x:v>25.027665</x:v>
+        <x:v>25.02766</x:v>
       </x:c>
       <x:c r="G9" s="25" t="n">
-        <x:v>305386.83</x:v>
+        <x:v>305387.04</x:v>
       </x:c>
       <x:c r="H9" s="25" t="n">
-        <x:v>2768954.02</x:v>
+        <x:v>2768953.47</x:v>
       </x:c>
       <x:c r="I9" s="26" t="n">
         <x:v>38</x:v>
@@ -1014,7 +1014,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O9" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303213007</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303213007</x:v>
       </x:c>
       <x:c r="P9" s="2" t="str">
         <x:v>2023-07-31</x:v>
@@ -1034,16 +1034,16 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>121.549049</x:v>
+        <x:v>121.54905</x:v>
       </x:c>
       <x:c r="F10" s="25" t="n">
-        <x:v>25.026752</x:v>
+        <x:v>25.02675</x:v>
       </x:c>
       <x:c r="G10" s="25" t="n">
-        <x:v>305409.55</x:v>
+        <x:v>305409.65</x:v>
       </x:c>
       <x:c r="H10" s="25" t="n">
-        <x:v>2768852.98</x:v>
+        <x:v>2768852.76</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
         <x:v>32</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="O10" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303221067</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303221067</x:v>
       </x:c>
       <x:c r="P10" s="2" t="str">
         <x:v>2023-07-31</x:v>
@@ -1084,13 +1084,13 @@
         <x:v>敦化南路二段</x:v>
       </x:c>
       <x:c r="E11" s="25" t="n">
-        <x:v>121.548446</x:v>
+        <x:v>121.54845</x:v>
       </x:c>
       <x:c r="F11" s="25" t="n">
         <x:v>25.02798</x:v>
       </x:c>
       <x:c r="G11" s="25" t="n">
-        <x:v>305348.14</x:v>
+        <x:v>305348.54</x:v>
       </x:c>
       <x:c r="H11" s="25" t="n">
         <x:v>2768988.76</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E4" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211358?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211358?photo=1</x:v>
       </x:c>
       <x:c r="F4" s="26" t="n">
         <x:v>0.6</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E5" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211358?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211358?photo=2</x:v>
       </x:c>
       <x:c r="F5" s="26" t="n">
         <x:v>12.6</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211358?photo=3</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211358?photo=3</x:v>
       </x:c>
       <x:c r="F6" s="26" t="n">
         <x:v>20.4</x:v>
@@ -1319,7 +1319,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211455?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211455?photo=1</x:v>
       </x:c>
       <x:c r="F8" s="26" t="n">
         <x:v>8.5</x:v>
@@ -1345,7 +1345,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211455?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211455?photo=2</x:v>
       </x:c>
       <x:c r="F9" s="26" t="n">
         <x:v>19.3</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E10" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303211455?photo=3</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303211455?photo=3</x:v>
       </x:c>
       <x:c r="F10" s="26" t="n">
         <x:v>9.3</x:v>
@@ -1419,7 +1419,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E12" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212037?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212037?photo=1</x:v>
       </x:c>
       <x:c r="F12" s="26" t="n">
         <x:v>14.3</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E13" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212037?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212037?photo=2</x:v>
       </x:c>
       <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
@@ -1471,7 +1471,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E14" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212037?photo=3</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212037?photo=3</x:v>
       </x:c>
       <x:c r="F14" s="26" t="n">
         <x:v>18.2</x:v>
@@ -1541,7 +1541,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E17" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212328?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212328?photo=1</x:v>
       </x:c>
       <x:c r="F17" s="26" t="n">
         <x:v>20.1</x:v>
@@ -1567,7 +1567,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E18" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212328?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212328?photo=2</x:v>
       </x:c>
       <x:c r="F18" s="26" t="n">
         <x:v>7.5</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303212425?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303212425?photo=1</x:v>
       </x:c>
       <x:c r="F20" s="26" t="n">
         <x:v>7</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E22" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303213007?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303213007?photo=1</x:v>
       </x:c>
       <x:c r="F22" s="26" t="n">
         <x:v>21.3</x:v>
@@ -1689,7 +1689,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E23" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303213007?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303213007?photo=2</x:v>
       </x:c>
       <x:c r="F23" s="26" t="n">
         <x:v>20.3</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E24" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303213007?photo=3</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303213007?photo=3</x:v>
       </x:c>
       <x:c r="F24" s="26" t="n">
         <x:v>6.4</x:v>
@@ -1763,7 +1763,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E26" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303221067?photo=1</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303221067?photo=1</x:v>
       </x:c>
       <x:c r="F26" s="26" t="n">
         <x:v>15.8</x:v>
@@ -1789,7 +1789,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E27" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303221067?photo=2</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303221067?photo=2</x:v>
       </x:c>
       <x:c r="F27" s="26" t="n">
         <x:v>2</x:v>
@@ -1815,7 +1815,7 @@
         <x:v>存活</x:v>
       </x:c>
       <x:c r="E28" s="2" t="str">
-        <x:v>https://preview.taipei-tree-twin.pages.dev/esg/#/tree/DA0303221067?photo=3</x:v>
+        <x:v>https://taipei-tree-twin.pages.dev/#/tree/DA0303221067?photo=3</x:v>
       </x:c>
       <x:c r="F28" s="26" t="n">
         <x:v>10.8</x:v>
